--- a/doc/CAST-BoM.xlsx
+++ b/doc/CAST-BoM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uconn-my.sharepoint.com/personal/anatol_gogoj_uconn_edu/Documents/Projects/CAST Spincoater/CAST/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0954CE2-968D-4ED9-BE40-38A167470482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{B0954CE2-968D-4ED9-BE40-38A167470482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8791BB0-0DE6-4333-99B6-7574A7CE3DD7}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15840" xr2:uid="{2C9C8878-50C9-4757-AAAF-D09075F65E78}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
   <si>
     <t>Designator</t>
   </si>
@@ -56,18 +56,9 @@
     <t>Source</t>
   </si>
   <si>
-    <t>PN_001</t>
-  </si>
-  <si>
-    <t>BLDC Motor - A2212 - 1800KV</t>
-  </si>
-  <si>
     <t>Amazon</t>
   </si>
   <si>
-    <t>PN_002</t>
-  </si>
-  <si>
     <t>Electronic Speed Controller &amp; DC Converter</t>
   </si>
   <si>
@@ -77,123 +68,30 @@
     <t>pkg</t>
   </si>
   <si>
-    <t>PN_004</t>
-  </si>
-  <si>
     <t>Hosyond ESP32-S3 USB-C</t>
   </si>
   <si>
-    <t>PN_005</t>
-  </si>
-  <si>
     <t>Hosyond Touch Screen</t>
   </si>
   <si>
-    <t>PN_006</t>
-  </si>
-  <si>
-    <t>XT60 Panel Passthrough</t>
-  </si>
-  <si>
-    <t>PN_007</t>
-  </si>
-  <si>
     <t>OVERTURE PETG Filament</t>
   </si>
   <si>
     <t>kg</t>
   </si>
   <si>
-    <t>PN_008</t>
-  </si>
-  <si>
     <t>Rubber Feet - 1/2" Round</t>
   </si>
   <si>
-    <t>PN_009</t>
-  </si>
-  <si>
     <t>M3 Countersunk Bolt Set</t>
   </si>
   <si>
-    <t>PN_010</t>
-  </si>
-  <si>
     <t>M3 Heat Set Inserts - D5xL4</t>
   </si>
   <si>
-    <t>PN_011</t>
-  </si>
-  <si>
-    <t>M3x12 bolts (screen)</t>
-  </si>
-  <si>
-    <t>Aliexpress</t>
-  </si>
-  <si>
-    <t>PN_012</t>
-  </si>
-  <si>
-    <t>100x100mm 3mm Transparent Plexiglass</t>
-  </si>
-  <si>
-    <t>PN_013</t>
-  </si>
-  <si>
-    <t>Soldering Tin Lead Free</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>PN_014</t>
-  </si>
-  <si>
-    <t>22AWG Cable (Black-Red)</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>PN_015</t>
-  </si>
-  <si>
-    <t>12V 5A - AC-DC Power adapter</t>
-  </si>
-  <si>
-    <t>PN_016</t>
-  </si>
-  <si>
-    <t>Hook and Loop Fastener Tape 20mm</t>
-  </si>
-  <si>
-    <t>PN_017</t>
-  </si>
-  <si>
-    <t>M3 X D4.2 X L5.0 Brass Hot Melt Insert Nuts</t>
-  </si>
-  <si>
-    <t>PN_018</t>
-  </si>
-  <si>
-    <t>M4x20 bolts - Countersunk Head</t>
-  </si>
-  <si>
-    <t>PN_019</t>
-  </si>
-  <si>
-    <t>M3x8 bolts - Countersunk Head</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Alternatives</t>
-  </si>
-  <si>
-    <t>Source of materials</t>
-  </si>
-  <si>
     <t>Hardware Tools</t>
   </si>
   <si>
@@ -237,6 +135,15 @@
   </si>
   <si>
     <t>Autodesk Fusion 360 (Optional)</t>
+  </si>
+  <si>
+    <t>BLDC Motor - A2212 - 930KV</t>
+  </si>
+  <si>
+    <t>5.5 x 2.1 Barrel Plug Panel Passthrough</t>
+  </si>
+  <si>
+    <t>AC - DC Power Supply 12V 10A</t>
   </si>
 </sst>
 </file>
@@ -246,7 +153,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot; &quot;&quot;$&quot;* #,##0.00&quot; &quot;;&quot; &quot;&quot;$&quot;* &quot;(&quot;#,##0.00&quot;)&quot;;&quot; &quot;&quot;$&quot;* &quot;-&quot;#&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -337,19 +244,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF1155CC"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF1155CC"/>
-      <name val="&quot;Arial&quot;"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Sans-serif"/>
@@ -362,7 +256,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,14 +323,8 @@
         <bgColor rgb="FFFFE599"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9DAF8"/>
-        <bgColor rgb="FFC9DAF8"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -552,23 +440,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -593,7 +472,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -605,7 +484,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -614,15 +493,8 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="15"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -639,21 +511,14 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="11" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent" xfId="8" xr:uid="{81AD2F56-4870-43FB-80D9-DDD59FFF4B8A}"/>
@@ -1006,16 +871,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C77B11CE-D938-43CE-AA16-BE91DC024051}">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="22" customWidth="1"/>
-    <col min="6" max="6" width="12.625" style="22" customWidth="1"/>
-    <col min="7" max="7" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="40.5" customWidth="1"/>
+    <col min="3" max="3" width="8.375" customWidth="1"/>
+    <col min="4" max="4" width="6.875" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="19" customWidth="1"/>
+    <col min="6" max="6" width="11.75" style="19" customWidth="1"/>
+    <col min="7" max="7" width="16.875" bestFit="1" customWidth="1"/>
     <col min="8" max="1023" width="13.375" customWidth="1"/>
     <col min="1024" max="1024" width="9.125" customWidth="1"/>
   </cols>
@@ -1045,11 +910,9 @@
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:8" ht="14.25">
-      <c r="A2" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
@@ -1059,20 +922,18 @@
         <v>12.99</v>
       </c>
       <c r="F2" s="9">
-        <f t="shared" ref="F2:F11" si="0">E2*C2</f>
+        <f t="shared" ref="F2:F12" si="0">E2*C2</f>
         <v>12.99</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" ht="14.25">
-      <c r="A3" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -1086,20 +947,20 @@
         <v>13.38</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="14.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" s="8">
         <v>8.7899999999999991</v>
@@ -1109,22 +970,20 @@
         <v>8.7899999999999991</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="14.25">
-      <c r="A5" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" s="8">
         <v>18.989999999999998</v>
@@ -1134,16 +993,14 @@
         <v>18.989999999999998</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="14.25">
-      <c r="A6" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -1157,45 +1014,43 @@
         <v>20.99</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="14.25">
-      <c r="A7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="6">
+      <c r="A7" s="5"/>
+      <c r="B7" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="25">
         <v>1</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8">
-        <v>9.69</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="D7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="23">
+        <v>6.99</v>
+      </c>
+      <c r="F7" s="23">
         <f t="shared" si="0"/>
-        <v>9.69</v>
+        <v>6.99</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="14.25">
-      <c r="A8" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E8" s="8">
         <v>12.29</v>
@@ -1205,22 +1060,20 @@
         <v>12.29</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="14.25">
-      <c r="A9" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E9" s="8">
         <v>4.95</v>
@@ -1230,22 +1083,20 @@
         <v>4.95</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="14.25">
-      <c r="A10" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E10" s="8">
         <v>8.89</v>
@@ -1255,434 +1106,163 @@
         <v>8.89</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" ht="14.25">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C11" s="6">
         <v>4</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="8">
-        <v>0.2</v>
+        <v>9.99</v>
       </c>
       <c r="F11" s="9">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>39.96</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="14.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
+      <c r="B12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
       <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="E12" s="8">
+        <v>20.99</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="0"/>
+        <v>20.99</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="14.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="14.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="14.25">
+      <c r="E15" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="18">
+        <f>SUM(F2:F14)</f>
+        <v>169.21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="18">
+      <c r="E17" s="20"/>
+    </row>
+    <row r="19" spans="2:5" ht="15">
+      <c r="B19" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="14.25">
+      <c r="B20" s="22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="14.25">
+      <c r="B21" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="14.25">
+      <c r="B22" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="14.25">
+      <c r="B23" s="22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="14.25">
+      <c r="B24" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="14.25">
+      <c r="B25" s="22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="14.25">
+      <c r="B26" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="14.25">
+      <c r="B27" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="14.25">
+      <c r="B28" s="22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="15">
+      <c r="B32" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="5" t="s">
+    </row>
+    <row r="33" spans="2:2" ht="14.25">
+      <c r="B33" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="6">
-        <v>4</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F13" s="9">
-        <f t="shared" ref="F13:F21" si="1">E13*C13</f>
-        <v>0.8</v>
-      </c>
-      <c r="G13" s="11" t="s">
+    </row>
+    <row r="34" spans="2:2" ht="14.25">
+      <c r="B34" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" ht="14.25">
-      <c r="A14" s="5" t="s">
+    </row>
+    <row r="35" spans="2:2" ht="14.25">
+      <c r="B35" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="5" t="s">
+    </row>
+    <row r="36" spans="2:2" ht="14.25">
+      <c r="B36" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="F14" s="9">
-        <f t="shared" si="1"/>
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" ht="14.25">
-      <c r="A15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="6">
-        <v>5</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="8">
-        <f>7.49/90</f>
-        <v>8.3222222222222225E-2</v>
-      </c>
-      <c r="F15" s="9">
-        <f t="shared" si="1"/>
-        <v>0.4161111111111111</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" ht="14.25">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="8">
-        <f>1.63/5</f>
-        <v>0.32599999999999996</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="1"/>
-        <v>0.13039999999999999</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25">
-      <c r="A17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8">
-        <v>10</v>
-      </c>
-      <c r="F17" s="9">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25">
-      <c r="A18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.17</v>
-      </c>
-      <c r="F18" s="9">
-        <f t="shared" si="1"/>
-        <v>0.317</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" ht="14.25">
-      <c r="A19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="6">
-        <v>6</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8">
-        <f>4.15/50</f>
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="F19" s="9">
-        <f t="shared" si="1"/>
-        <v>0.498</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" ht="14.25">
-      <c r="A20" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8">
-        <v>0.12</v>
-      </c>
-      <c r="F20" s="9">
-        <f t="shared" si="1"/>
-        <v>0.24</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" ht="14.25">
-      <c r="A21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="6">
-        <v>3</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8">
-        <v>0.03</v>
-      </c>
-      <c r="F21" s="9">
-        <f t="shared" si="1"/>
-        <v>0.09</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" ht="14.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" ht="14.25">
-      <c r="E23" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="21">
-        <f>SUM(F2:F22)</f>
-        <v>128.48151111111108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="18">
-      <c r="E25" s="23"/>
-    </row>
-    <row r="26" spans="1:8" ht="14.25">
-      <c r="B26" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="14.25">
-      <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="14.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="14.25">
-      <c r="A29" s="26"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="27"/>
-    </row>
-    <row r="30" spans="1:8" ht="14.25">
-      <c r="A30" s="26"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="27"/>
-    </row>
-    <row r="31" spans="1:8" ht="14.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="29"/>
-    </row>
-    <row r="34" spans="2:2" ht="15">
-      <c r="B34" s="31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="14.25">
-      <c r="B35" s="32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" ht="14.25">
-      <c r="B36" s="32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" ht="14.25">
-      <c r="B37" s="32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" ht="14.25">
-      <c r="B38" s="32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" ht="14.25">
-      <c r="B39" s="32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" ht="14.25">
-      <c r="B40" s="32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" ht="14.25">
-      <c r="B41" s="32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" ht="14.25">
-      <c r="B42" s="32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" ht="14.25">
-      <c r="B43" s="32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" ht="15">
-      <c r="B47" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" ht="14.25">
-      <c r="B48" s="32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" ht="14.25">
-      <c r="B49" s="32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" ht="14.25">
-      <c r="B50" s="32" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" ht="14.25">
-      <c r="B51" s="32" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" ht="14.25">
-      <c r="B52" s="33"/>
-    </row>
-    <row r="53" spans="2:2" ht="14.25">
-      <c r="B53" s="33"/>
-    </row>
-    <row r="54" spans="2:2" ht="14.25">
-      <c r="B54" s="33"/>
-    </row>
-    <row r="55" spans="2:2" ht="14.25">
-      <c r="B55" s="33"/>
-    </row>
+    </row>
+    <row r="37" spans="2:2" ht="14.25"/>
+    <row r="38" spans="2:2" ht="14.25"/>
+    <row r="39" spans="2:2" ht="14.25"/>
+    <row r="40" spans="2:2" ht="14.25"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{0F15A467-E44C-4D13-8643-5B223BCC692D}"/>
@@ -1690,21 +1270,12 @@
     <hyperlink ref="G4" r:id="rId3" xr:uid="{61653BFC-8786-402E-9392-F53FBFE3E7CD}"/>
     <hyperlink ref="G5" r:id="rId4" xr:uid="{3A185130-B314-4ACA-8F47-EAA6BB422DEE}"/>
     <hyperlink ref="G6" r:id="rId5" xr:uid="{7E51B9F1-220F-420B-879E-57BADA11EB3B}"/>
-    <hyperlink ref="G7" r:id="rId6" xr:uid="{ACA614B9-1A87-4E8B-A69C-5F87B845AA08}"/>
-    <hyperlink ref="G8" r:id="rId7" xr:uid="{C347481E-7FC4-488F-A0A4-3B628E650327}"/>
-    <hyperlink ref="G9" r:id="rId8" xr:uid="{C158721E-76DC-4687-9E95-868D390A4380}"/>
-    <hyperlink ref="G10" r:id="rId9" xr:uid="{B29BFA60-BCF5-4F10-8BD8-16A017D55731}"/>
-    <hyperlink ref="G11" r:id="rId10" xr:uid="{9B4D5FB6-B9C6-4047-94E5-7B484E6C1869}"/>
-    <hyperlink ref="G13" r:id="rId11" xr:uid="{2FAD068B-296B-4FE0-ADC1-DE2925D97246}"/>
-    <hyperlink ref="G14" r:id="rId12" xr:uid="{E982B6F9-C8F6-4F0A-A8FE-0F18A9DC3103}"/>
-    <hyperlink ref="G15" r:id="rId13" xr:uid="{84790A5F-FB61-4FB2-9566-8E061726A05D}"/>
-    <hyperlink ref="G16" r:id="rId14" xr:uid="{DAF5CB64-133F-4CD3-835B-9E580723CD5C}"/>
-    <hyperlink ref="G17" r:id="rId15" xr:uid="{848C19E2-F931-49E6-9EF3-A518AE0EAEF3}"/>
-    <hyperlink ref="G18" r:id="rId16" xr:uid="{9C4C6BA2-5E0F-4046-B457-F88EC468F654}"/>
-    <hyperlink ref="G19" r:id="rId17" xr:uid="{7BE5D1DA-57D3-4DAD-845D-FAA42EB515D6}"/>
-    <hyperlink ref="G20" r:id="rId18" xr:uid="{DDE2ACDA-68C8-4872-948E-74603091819E}"/>
-    <hyperlink ref="G21" r:id="rId19" xr:uid="{CF0E5600-4C5A-400D-9D9D-039E4F40EA2B}"/>
-    <hyperlink ref="G28" r:id="rId20" xr:uid="{BBC5580D-BE40-4A1F-8326-883D24A018C8}"/>
+    <hyperlink ref="G8" r:id="rId6" xr:uid="{C347481E-7FC4-488F-A0A4-3B628E650327}"/>
+    <hyperlink ref="G9" r:id="rId7" xr:uid="{C158721E-76DC-4687-9E95-868D390A4380}"/>
+    <hyperlink ref="G10" r:id="rId8" xr:uid="{B29BFA60-BCF5-4F10-8BD8-16A017D55731}"/>
+    <hyperlink ref="G11" r:id="rId9" xr:uid="{9B4D5FB6-B9C6-4047-94E5-7B484E6C1869}"/>
+    <hyperlink ref="G7" r:id="rId10" xr:uid="{1397FBB9-E7ED-42AB-AB51-CDC4124B2B63}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{4EDEDFE8-25B4-4EED-B496-BE571B198C3B}"/>
   </hyperlinks>
   <pageMargins left="0.74805555555555614" right="0.74805555555555614" top="1.3776388888888891" bottom="1.3776388888888891" header="0.98388888888888903" footer="0.98388888888888903"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
